--- a/cotacoes/2026-09-08/fechamento/PEDIDO_MEDCENTRO_09-09-2026.xlsx
+++ b/cotacoes/2026-09-08/fechamento/PEDIDO_MEDCENTRO_09-09-2026.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -899,7 +899,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.6% (aceito, lim 5%)</t>
+          <t>REAJUSTE +1.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -1968,7 +1968,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Pedido FINAL MEDCENTRO — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: preço até 5% acima da referência (últ. compra; sem ela, menor histórico), 10% quando o item está zerado. 'Qtd pedido' na embalagem do fornecedor.</t>
+          <t>Pedido FINAL MEDCENTRO — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: teto de reajuste de 4% sobre a última compra OU 6% sobre a média histórica (3/6/12m). 'Qtd pedido' na embalagem do fornecedor.</t>
         </is>
       </c>
     </row>
